--- a/Assay Exchanges - Low Silver Sinchi 1.xlsx
+++ b/Assay Exchanges - Low Silver Sinchi 1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a5dd0d63cd58a577/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\claude\SMPY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="620" documentId="8_{5EBE54FA-2F31-4C9A-BA29-B6794EB02023}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1CC1FD0A-D0FE-4AC3-82EA-042C8E13D6EE}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{810DAC67-F691-409E-8108-EACE935162D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19890" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="543" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6344,6 +6344,21 @@
       <c r="E124" s="8" t="s">
         <v>6</v>
       </c>
+      <c r="F124">
+        <v>3722</v>
+      </c>
+      <c r="G124">
+        <v>11.62</v>
+      </c>
+      <c r="I124">
+        <v>0.68</v>
+      </c>
+      <c r="J124">
+        <v>0.91</v>
+      </c>
+      <c r="K124">
+        <v>0.75</v>
+      </c>
     </row>
     <row r="125" spans="1:13">
       <c r="A125" s="7" t="s">

--- a/Assay Exchanges - Low Silver Sinchi 1.xlsx
+++ b/Assay Exchanges - Low Silver Sinchi 1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\claude\SMPY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{810DAC67-F691-409E-8108-EACE935162D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4A15443-B957-466A-BE2B-9B99D469F9CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19890" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="543" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="56025" yWindow="-105" windowWidth="29070" windowHeight="15750" tabRatio="543" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="16" r:id="rId1"/>
@@ -2517,10 +2517,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A530310-9BA1-42B9-91C0-4E0C6223A490}">
   <dimension ref="A1:N139"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="12.53125" customWidth="1"/>
-    <col min="3" max="3" width="11.86328125" customWidth="1"/>
+    <col min="1" max="1" width="12.5546875" customWidth="1"/>
+    <col min="3" max="3" width="11.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -2829,7 +2829,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:13" ht="27.6">
       <c r="A11" s="2" t="s">
         <v>8</v>
       </c>
@@ -2865,7 +2865,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="27">
+    <row r="12" spans="1:13" ht="27.6">
       <c r="A12" s="2" t="s">
         <v>8</v>
       </c>
@@ -3053,7 +3053,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="18" spans="1:13">
+    <row r="18" spans="1:13" ht="27.6">
       <c r="A18" s="2" t="s">
         <v>9</v>
       </c>
@@ -3094,7 +3094,7 @@
         <v>0.56999999999999995</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="27">
+    <row r="19" spans="1:13" ht="27.6">
       <c r="A19" s="2" t="s">
         <v>9</v>
       </c>
@@ -3260,7 +3260,7 @@
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
     </row>
-    <row r="24" spans="1:13">
+    <row r="24" spans="1:13" ht="27.6">
       <c r="A24" s="7" t="s">
         <v>10</v>
       </c>
@@ -3427,7 +3427,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="29" spans="1:13">
+    <row r="29" spans="1:13" ht="27.6">
       <c r="A29" s="7" t="s">
         <v>12</v>
       </c>
@@ -3468,7 +3468,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="30" spans="1:13" ht="27">
+    <row r="30" spans="1:13" ht="27.6">
       <c r="A30" s="7" t="s">
         <v>12</v>
       </c>
@@ -3698,7 +3698,7 @@
       <c r="L45" s="4"/>
       <c r="M45" s="4"/>
     </row>
-    <row r="46" spans="1:13">
+    <row r="46" spans="1:13" ht="27.6">
       <c r="A46" s="7" t="s">
         <v>5</v>
       </c>
@@ -3865,7 +3865,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="51" spans="1:14">
+    <row r="51" spans="1:14" ht="27.6">
       <c r="A51" s="7" t="s">
         <v>13</v>
       </c>
@@ -3906,7 +3906,7 @@
         <v>0.67</v>
       </c>
     </row>
-    <row r="52" spans="1:14" ht="27">
+    <row r="52" spans="1:14" ht="27.6">
       <c r="A52" s="7" t="s">
         <v>13</v>
       </c>
@@ -4078,7 +4078,7 @@
         <v>12.41</v>
       </c>
     </row>
-    <row r="58" spans="1:14">
+    <row r="58" spans="1:14" ht="27.6">
       <c r="A58" s="7" t="s">
         <v>41</v>
       </c>
@@ -4119,7 +4119,7 @@
         <v>1.0900000000000001</v>
       </c>
     </row>
-    <row r="59" spans="1:14" ht="27">
+    <row r="59" spans="1:14" ht="27.6">
       <c r="A59" s="7" t="s">
         <v>41</v>
       </c>
@@ -4300,7 +4300,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="65" spans="1:13">
+    <row r="65" spans="1:13" ht="27.6">
       <c r="A65" s="7" t="s">
         <v>14</v>
       </c>
@@ -4341,7 +4341,7 @@
         <v>0.65</v>
       </c>
     </row>
-    <row r="66" spans="1:13" ht="27">
+    <row r="66" spans="1:13" ht="27.6">
       <c r="A66" s="7" t="s">
         <v>14</v>
       </c>
@@ -4528,7 +4528,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="72" spans="1:13">
+    <row r="72" spans="1:13" ht="27.6">
       <c r="A72" s="7" t="s">
         <v>42</v>
       </c>
@@ -4569,7 +4569,7 @@
         <v>0.89</v>
       </c>
     </row>
-    <row r="73" spans="1:13" ht="27">
+    <row r="73" spans="1:13" ht="27.6">
       <c r="A73" s="7" t="s">
         <v>42</v>
       </c>
@@ -4768,7 +4768,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="79" spans="1:13">
+    <row r="79" spans="1:13" ht="27.6">
       <c r="A79" s="7" t="s">
         <v>43</v>
       </c>
@@ -4809,7 +4809,7 @@
         <v>0.89</v>
       </c>
     </row>
-    <row r="80" spans="1:13" ht="27">
+    <row r="80" spans="1:13" ht="27.6">
       <c r="A80" s="7" t="s">
         <v>43</v>
       </c>
@@ -5011,7 +5011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:13">
+    <row r="86" spans="1:13" ht="27.6">
       <c r="A86" s="7" t="s">
         <v>15</v>
       </c>
@@ -5052,7 +5052,7 @@
         <v>1.1399999999999999</v>
       </c>
     </row>
-    <row r="87" spans="1:13" ht="27">
+    <row r="87" spans="1:13" ht="27.6">
       <c r="A87" s="7" t="s">
         <v>15</v>
       </c>
@@ -5251,7 +5251,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="93" spans="1:13">
+    <row r="93" spans="1:13" ht="27.6">
       <c r="A93" s="7" t="s">
         <v>16</v>
       </c>
@@ -5292,7 +5292,7 @@
         <v>0.71</v>
       </c>
     </row>
-    <row r="94" spans="1:13" ht="27">
+    <row r="94" spans="1:13" ht="27.6">
       <c r="A94" s="7" t="s">
         <v>16</v>
       </c>
@@ -5497,7 +5497,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="100" spans="1:13">
+    <row r="100" spans="1:13" ht="27.6">
       <c r="A100" s="7" t="s">
         <v>17</v>
       </c>
@@ -5538,7 +5538,7 @@
         <v>1.03</v>
       </c>
     </row>
-    <row r="101" spans="1:13" ht="27">
+    <row r="101" spans="1:13" ht="27.6">
       <c r="A101" s="7" t="s">
         <v>17</v>
       </c>
@@ -5737,7 +5737,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="107" spans="1:13">
+    <row r="107" spans="1:13" ht="27.6">
       <c r="A107" s="7" t="s">
         <v>18</v>
       </c>
@@ -5775,7 +5775,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="108" spans="1:13" ht="27">
+    <row r="108" spans="1:13" ht="27.6">
       <c r="A108" s="7" t="s">
         <v>18</v>
       </c>
@@ -5971,7 +5971,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="114" spans="1:13">
+    <row r="114" spans="1:13" ht="27.6">
       <c r="A114" s="7" t="s">
         <v>44</v>
       </c>
@@ -6012,7 +6012,7 @@
         <v>1.03</v>
       </c>
     </row>
-    <row r="115" spans="1:13" ht="27">
+    <row r="115" spans="1:13" ht="27.6">
       <c r="A115" s="7" t="s">
         <v>44</v>
       </c>
@@ -6211,7 +6211,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="121" spans="1:13">
+    <row r="121" spans="1:13" ht="27.6">
       <c r="A121" s="7" t="s">
         <v>45</v>
       </c>
@@ -6252,7 +6252,7 @@
         <v>0.81</v>
       </c>
     </row>
-    <row r="122" spans="1:13" ht="27">
+    <row r="122" spans="1:13" ht="27.6">
       <c r="A122" s="7" t="s">
         <v>45</v>
       </c>
@@ -6375,6 +6375,21 @@
       </c>
       <c r="E125" s="10" t="s">
         <v>11</v>
+      </c>
+      <c r="F125">
+        <v>3267</v>
+      </c>
+      <c r="G125">
+        <v>9.8800000000000008</v>
+      </c>
+      <c r="I125">
+        <v>0.67</v>
+      </c>
+      <c r="J125">
+        <v>0.83</v>
+      </c>
+      <c r="K125">
+        <v>0.78</v>
       </c>
     </row>
     <row r="126" spans="1:13">
@@ -6424,7 +6439,7 @@
         <v>0.31</v>
       </c>
     </row>
-    <row r="128" spans="1:13">
+    <row r="128" spans="1:13" ht="27.6">
       <c r="A128" s="7" t="s">
         <v>46</v>
       </c>
@@ -6456,7 +6471,7 @@
         <v>0.52</v>
       </c>
     </row>
-    <row r="129" spans="1:13" ht="27">
+    <row r="129" spans="1:13" ht="27.6">
       <c r="A129" s="7" t="s">
         <v>46</v>
       </c>
@@ -6622,7 +6637,7 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="135" spans="1:13">
+    <row r="135" spans="1:13" ht="27.6">
       <c r="A135" s="7" t="s">
         <v>48</v>
       </c>
@@ -6654,7 +6669,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="136" spans="1:13" ht="27">
+    <row r="136" spans="1:13" ht="27.6">
       <c r="A136" s="7" t="s">
         <v>48</v>
       </c>
